--- a/Calculadora_Lucro_Wallacy.xlsx
+++ b/Calculadora_Lucro_Wallacy.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
